--- a/Praktikum 2_Metode Numerik - Sistem Persamaan Linier.xlsx
+++ b/Praktikum 2_Metode Numerik - Sistem Persamaan Linier.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Maria\Github\Metode-Numerik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0EEDBF-8B5A-41CC-AF1D-3B00D9B2D535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175DAC7D-7BE0-4E85-BBAE-754A7C873644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3E7814A2-7EF8-412E-A7AA-8F3F989192BC}"/>
+    <workbookView xWindow="1060" yWindow="1060" windowWidth="14400" windowHeight="7270" xr2:uid="{3E7814A2-7EF8-412E-A7AA-8F3F989192BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -207,69 +207,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5905,189 +5904,186 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79160A0-0197-44CA-B9AE-4A09DB2205B4}">
   <dimension ref="A2:S67"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="16384" width="8.7265625" style="5"/>
-  </cols>
   <sheetData>
     <row r="2" spans="1:10" ht="24.5" x14ac:dyDescent="0.65">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7" t="s">
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="10"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
     </row>
     <row r="13" spans="1:10" ht="26" x14ac:dyDescent="0.35">
-      <c r="A13" s="10"/>
-      <c r="B13" s="28" t="s">
+      <c r="A13" s="4"/>
+      <c r="B13" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
     </row>
     <row r="14" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20" t="s">
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
     </row>
     <row r="15" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B15" s="27"/>
-      <c r="C15" s="21" t="s">
+      <c r="B15" s="20"/>
+      <c r="C15" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="G15" s="21" t="s">
+      <c r="G15" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H15" s="21" t="s">
+      <c r="H15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I15" s="21" t="s">
+      <c r="I15" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J15" s="21" t="s">
+      <c r="J15" s="12" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="11">
+      <c r="B16" s="5">
         <v>0</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="6">
         <v>0</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="6">
         <v>0</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="6">
         <v>0</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="6">
         <v>0</v>
       </c>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B17" s="11">
+      <c r="B17" s="5">
         <v>1</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="7">
         <f xml:space="preserve"> (6+D16-2*E16)/10</f>
         <v>0.6</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="6">
         <f xml:space="preserve"> (25 + C16+E16-3*F16)/11</f>
         <v>2.2727272727272729</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="6">
         <f xml:space="preserve"> (-11 -2*C16+D16+F16)/10</f>
         <v>-1.1000000000000001</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="6">
         <f xml:space="preserve"> (15 -3*D16+E16)/8</f>
         <v>1.875</v>
       </c>
@@ -6109,22 +6105,22 @@
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B18" s="11">
+      <c r="B18" s="5">
         <v>2</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="8">
         <f t="shared" ref="C18:C26" si="1" xml:space="preserve"> (6+D17-2*E17)/10</f>
         <v>1.0472727272727274</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="6">
         <f t="shared" ref="D18:D26" si="2" xml:space="preserve"> (25 + C17+E17-3*F17)/11</f>
         <v>1.7159090909090908</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="6">
         <f t="shared" ref="E18:E26" si="3" xml:space="preserve"> (-11 -2*C17+D17+F17)/10</f>
         <v>-0.80522727272727257</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="6">
         <f t="shared" ref="F18:F26" si="4" xml:space="preserve"> (15 -3*D17+E17)/8</f>
         <v>0.88522727272727275</v>
       </c>
@@ -6146,22 +6142,22 @@
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B19" s="11">
+      <c r="B19" s="5">
         <v>3</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="8">
         <f t="shared" si="1"/>
         <v>0.9326363636363636</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="6">
         <f t="shared" si="2"/>
         <v>2.0533057851239671</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="6">
         <f t="shared" si="3"/>
         <v>-1.0493409090909092</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="6">
         <f t="shared" si="4"/>
         <v>1.1308806818181818</v>
       </c>
@@ -6183,22 +6179,22 @@
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B20" s="11">
+      <c r="B20" s="5">
         <v>4</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="8">
         <f t="shared" si="1"/>
         <v>1.0151987603305785</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="6">
         <f t="shared" si="2"/>
         <v>1.9536957644628101</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="6">
         <f t="shared" si="3"/>
         <v>-0.9681086260330577</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="6">
         <f t="shared" si="4"/>
         <v>0.97384271694214875</v>
       </c>
@@ -6218,27 +6214,27 @@
         <f t="shared" si="8"/>
         <v>0.16125598327533822</v>
       </c>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="15"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B21" s="11">
+      <c r="B21" s="5">
         <v>5</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="8">
         <f t="shared" si="1"/>
         <v>0.98899130165289262</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="6">
         <f t="shared" si="2"/>
         <v>2.0114147257700976</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="6">
         <f t="shared" si="3"/>
         <v>-1.0102859039256198</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="6">
         <f t="shared" si="4"/>
         <v>1.0213505100723141</v>
       </c>
@@ -6258,27 +6254,27 @@
         <f t="shared" si="8"/>
         <v>4.651468096569681E-2</v>
       </c>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B22" s="11">
+      <c r="B22" s="5">
         <v>6</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="8">
         <f t="shared" si="1"/>
         <v>1.003198653362134</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="6">
         <f t="shared" si="2"/>
         <v>1.9922412606827571</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="6">
         <f t="shared" si="3"/>
         <v>-0.99452173674633748</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="6">
         <f t="shared" si="4"/>
         <v>0.99443373984551098</v>
       </c>
@@ -6298,27 +6294,27 @@
         <f t="shared" si="8"/>
         <v>2.7067434609554568E-2</v>
       </c>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B23" s="11">
+      <c r="B23" s="5">
         <v>7</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="8">
         <f t="shared" si="1"/>
         <v>0.99812847341754318</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="6">
         <f t="shared" si="2"/>
         <v>2.0023068815526606</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="6">
         <f t="shared" si="3"/>
         <v>-1.0019722306195997</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="6">
         <f t="shared" si="4"/>
         <v>1.0035943101506739</v>
       </c>
@@ -6340,22 +6336,22 @@
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B24" s="11">
+      <c r="B24" s="5">
         <v>8</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="8">
         <f t="shared" si="1"/>
         <v>1.0006251342791859</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="6">
         <f t="shared" si="2"/>
         <v>1.9986703011223563</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="6">
         <f t="shared" si="3"/>
         <v>-0.99903557551317501</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="6">
         <f t="shared" si="4"/>
         <v>0.99888839059030232</v>
       </c>
@@ -6377,174 +6373,174 @@
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B25" s="22">
+      <c r="B25" s="13">
         <v>9</v>
       </c>
-      <c r="C25" s="23">
+      <c r="C25" s="14">
         <f t="shared" si="1"/>
         <v>0.99967414521487064</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="15">
         <f t="shared" si="2"/>
         <v>2.0004476715450092</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="15">
         <f t="shared" si="3"/>
         <v>-1.0003691576845715</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="15">
         <f t="shared" si="4"/>
         <v>1.0006191901399695</v>
       </c>
-      <c r="G25" s="25">
+      <c r="G25" s="16">
         <f t="shared" si="5"/>
         <v>9.5129904966265459E-4</v>
       </c>
-      <c r="H25" s="25">
+      <c r="H25" s="16">
         <f t="shared" si="6"/>
         <v>8.8848633630101077E-4</v>
       </c>
-      <c r="I25" s="25">
+      <c r="I25" s="16">
         <f t="shared" si="7"/>
         <v>1.3330900509599148E-3</v>
       </c>
-      <c r="J25" s="25">
+      <c r="J25" s="16">
         <f t="shared" si="8"/>
         <v>1.7297285188234708E-3</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B26" s="22">
+      <c r="B26" s="13">
         <v>10</v>
       </c>
-      <c r="C26" s="23">
+      <c r="C26" s="14">
         <f t="shared" si="1"/>
         <v>1.0001185986914152</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="15">
         <f t="shared" si="2"/>
         <v>1.9997679470100358</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="15">
         <f t="shared" si="3"/>
         <v>-0.9998281428744763</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="15">
         <f t="shared" si="4"/>
         <v>0.99978597846005013</v>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="16">
         <f t="shared" si="5"/>
         <v>4.4440077119460981E-4</v>
       </c>
-      <c r="H26" s="25">
+      <c r="H26" s="16">
         <f t="shared" si="6"/>
         <v>3.399017050902036E-4</v>
       </c>
-      <c r="I26" s="25">
+      <c r="I26" s="16">
         <f t="shared" si="7"/>
         <v>5.4110780332684209E-4</v>
       </c>
-      <c r="J26" s="25">
+      <c r="J26" s="16">
         <f t="shared" si="8"/>
         <v>8.3339004333979794E-4</v>
       </c>
     </row>
     <row r="30" spans="2:16" ht="26" x14ac:dyDescent="0.35">
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
     </row>
     <row r="31" spans="2:16" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20" t="s">
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
     </row>
     <row r="32" spans="2:16" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B32" s="27"/>
-      <c r="C32" s="21" t="s">
+      <c r="B32" s="20"/>
+      <c r="C32" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="21" t="s">
+      <c r="F32" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="G32" s="21" t="s">
+      <c r="G32" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H32" s="21" t="s">
+      <c r="H32" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I32" s="21" t="s">
+      <c r="I32" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="21" t="s">
+      <c r="J32" s="12" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B33" s="11">
+      <c r="B33" s="5">
         <v>0</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="6">
         <v>0</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="6">
         <v>0</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="6">
         <v>0</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="6">
         <v>0</v>
       </c>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B34" s="11">
+      <c r="B34" s="5">
         <v>1</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="6">
         <f xml:space="preserve"> (6+D33-2*E33)/10</f>
         <v>0.6</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="6">
         <f xml:space="preserve"> (25 + C34 + E33- 3*F33)/11</f>
         <v>2.3272727272727276</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="6">
         <f xml:space="preserve"> (-11 - 2*C34 + D34 + F33)/10</f>
         <v>-0.98727272727272708</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="6">
         <f xml:space="preserve"> (15- 3*D34 + E34)/8</f>
         <v>0.87886363636363629</v>
       </c>
@@ -6566,22 +6562,22 @@
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B35" s="11">
+      <c r="B35" s="5">
         <v>2</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="6">
         <f t="shared" ref="C35:C37" si="10" xml:space="preserve"> (6+D34-2*E34)/10</f>
         <v>1.0301818181818183</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="6">
         <f t="shared" ref="D35:D37" si="11" xml:space="preserve"> (25 + C35 + E34- 3*F34)/11</f>
         <v>2.0369380165289255</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="6">
         <f t="shared" ref="E35:E37" si="12" xml:space="preserve"> (-11 - 2*C35 + D35 + F34)/10</f>
         <v>-1.0144561983471074</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="6">
         <f t="shared" ref="F35:F37" si="13" xml:space="preserve"> (15- 3*D35 + E35)/8</f>
         <v>0.98434121900826443</v>
       </c>
@@ -6603,22 +6599,22 @@
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B36" s="11">
+      <c r="B36" s="5">
         <v>3</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="6">
         <f t="shared" si="10"/>
         <v>1.0065850413223141</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="6">
         <f t="shared" si="11"/>
         <v>2.003555016904583</v>
       </c>
-      <c r="E36" s="12">
+      <c r="E36" s="6">
         <f t="shared" si="12"/>
         <v>-1.0025273846731779</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="6">
         <f t="shared" si="13"/>
         <v>0.99835094557663417</v>
       </c>
@@ -6640,22 +6636,22 @@
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B37" s="11">
+      <c r="B37" s="5">
         <v>4</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="6">
         <f t="shared" si="10"/>
         <v>1.0008609786250939</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="6">
         <f t="shared" si="11"/>
         <v>2.000298250656547</v>
       </c>
-      <c r="E37" s="12">
+      <c r="E37" s="6">
         <f t="shared" si="12"/>
         <v>-1.0003072761017007</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F37" s="6">
         <f t="shared" si="13"/>
         <v>0.99984974649108227</v>
       </c>
@@ -6677,211 +6673,211 @@
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B38" s="22">
+      <c r="B38" s="13">
         <v>5</v>
       </c>
-      <c r="C38" s="24">
+      <c r="C38" s="15">
         <f xml:space="preserve"> (6+D37-2*E37)/10</f>
         <v>1.0000912802859949</v>
       </c>
-      <c r="D38" s="24">
+      <c r="D38" s="15">
         <f xml:space="preserve"> (25 + C38 + E37- 3*F37)/11</f>
         <v>2.000021342246459</v>
       </c>
-      <c r="E38" s="24">
+      <c r="E38" s="15">
         <f xml:space="preserve"> (-11 - 2*C38 + D38 + F37)/10</f>
         <v>-1.0000311471834449</v>
       </c>
-      <c r="F38" s="24">
+      <c r="F38" s="15">
         <f xml:space="preserve"> (15- 3*D38 + E38)/8</f>
         <v>0.99998810325964727</v>
       </c>
-      <c r="G38" s="25">
+      <c r="G38" s="16">
         <f xml:space="preserve"> ABS(($C$34 - $C$33)/$C$34)</f>
         <v>1</v>
       </c>
-      <c r="H38" s="25">
+      <c r="H38" s="16">
         <f t="shared" si="15"/>
         <v>1.3845272759787421E-4</v>
       </c>
-      <c r="I38" s="25">
+      <c r="I38" s="16">
         <f t="shared" si="16"/>
         <v>2.7612031788559727E-4</v>
       </c>
-      <c r="J38" s="25">
+      <c r="J38" s="16">
         <f xml:space="preserve"> ABS((F38 - F37)/F38)</f>
         <v>1.3835841457912943E-4</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B39" s="22">
+      <c r="B39" s="13">
         <v>6</v>
       </c>
-      <c r="C39" s="24">
+      <c r="C39" s="15">
         <f xml:space="preserve"> (6+D38-2*E38)/10</f>
         <v>1.0000083636613348</v>
       </c>
-      <c r="D39" s="24">
+      <c r="D39" s="15">
         <f xml:space="preserve"> (25 + C39 + E38- 3*F38)/11</f>
         <v>2.0000011733362677</v>
       </c>
-      <c r="E39" s="24">
+      <c r="E39" s="15">
         <f xml:space="preserve"> (-11 - 2*C39 + D39 + F38)/10</f>
         <v>-1.0000027450726754</v>
       </c>
-      <c r="F39" s="24">
+      <c r="F39" s="15">
         <f xml:space="preserve"> (15- 3*D39 + E39)/8</f>
         <v>0.99999921686481508</v>
       </c>
-      <c r="G39" s="25">
+      <c r="G39" s="16">
         <f xml:space="preserve"> ABS(($C$34 - $C$33)/$C$34)</f>
         <v>1</v>
       </c>
-      <c r="H39" s="25">
+      <c r="H39" s="16">
         <f t="shared" si="15"/>
         <v>1.0084449179424167E-5</v>
       </c>
-      <c r="I39" s="25">
+      <c r="I39" s="16">
         <f t="shared" si="16"/>
         <v>2.8402032803843446E-5</v>
       </c>
-      <c r="J39" s="25">
+      <c r="J39" s="16">
         <f xml:space="preserve"> ABS((F39 - F38)/F39)</f>
         <v>1.1113613871273845E-5</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A45" s="16"/>
-      <c r="B45" s="16"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="16"/>
-      <c r="J45" s="16"/>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="16"/>
-      <c r="O45" s="16"/>
-      <c r="P45" s="16"/>
-      <c r="Q45" s="16"/>
-      <c r="R45" s="16"/>
-      <c r="S45" s="16"/>
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="F47" s="5" t="s">
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="F47" t="s">
         <v>15</v>
       </c>
-      <c r="G47" s="5">
+      <c r="G47">
         <v>1.25</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="18"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
     </row>
     <row r="49" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="18"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="18"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B50" s="18"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
     </row>
     <row r="52" spans="2:10" ht="26" x14ac:dyDescent="0.35">
-      <c r="B52" s="28" t="s">
+      <c r="B52" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="26"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
     </row>
     <row r="53" spans="2:10" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="20" t="s">
+      <c r="C53" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20" t="s">
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="G53" s="20"/>
-      <c r="H53" s="20"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
     </row>
     <row r="54" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="27"/>
-      <c r="C54" s="21" t="s">
+      <c r="B54" s="20"/>
+      <c r="C54" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D54" s="21" t="s">
+      <c r="D54" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="21" t="s">
+      <c r="E54" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="21" t="s">
+      <c r="F54" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G54" s="21" t="s">
+      <c r="G54" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H54" s="21" t="s">
+      <c r="H54" s="12" t="s">
         <v>8</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B55" s="11">
+      <c r="B55" s="5">
         <v>0</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="6">
         <v>0</v>
       </c>
-      <c r="D55" s="12">
+      <c r="D55" s="6">
         <v>0</v>
       </c>
-      <c r="E55" s="12">
+      <c r="E55" s="6">
         <v>0</v>
       </c>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B56" s="11">
+      <c r="B56" s="5">
         <v>1</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="6">
         <f xml:space="preserve"> ((1-$G$47)*C55 + $G$47/4 * (24 - 3*D55))</f>
         <v>7.5</v>
       </c>
-      <c r="D56" s="12">
+      <c r="D56" s="6">
         <f xml:space="preserve"> ((1 - $G$47)*D55 + $G$47/4 * (30 - 3*C56 + E55))</f>
         <v>2.34375</v>
       </c>
-      <c r="E56" s="12">
+      <c r="E56" s="6">
         <f xml:space="preserve"> ((1 - $G$47)*E55 + $G$47/4 * (-24 + D56))</f>
         <v>-6.767578125</v>
       </c>
@@ -6899,18 +6895,18 @@
       </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B57" s="11">
+      <c r="B57" s="5">
         <v>2</v>
       </c>
-      <c r="C57" s="12">
+      <c r="C57" s="6">
         <f t="shared" ref="C57:C64" si="18" xml:space="preserve"> ((1-$G$47)*C56 + $G$47/4 * (24 - 3*D56))</f>
         <v>3.427734375</v>
       </c>
-      <c r="D57" s="12">
+      <c r="D57" s="6">
         <f t="shared" ref="D57:D64" si="19" xml:space="preserve"> ((1 - $G$47)*D56 + $G$47/4 * (30 - 3*C57 + E56))</f>
         <v>3.460693359375</v>
       </c>
-      <c r="E57" s="12">
+      <c r="E57" s="6">
         <f t="shared" ref="E57:E64" si="20" xml:space="preserve"> ((1 - $G$47)*E56 + $G$47/4 * (-24 + D57))</f>
         <v>-4.7266387939453125</v>
       </c>
@@ -6928,18 +6924,18 @@
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B58" s="11">
+      <c r="B58" s="5">
         <v>3</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C58" s="6">
         <f t="shared" si="18"/>
         <v>3.3986663818359375</v>
       </c>
-      <c r="D58" s="12">
+      <c r="D58" s="6">
         <f t="shared" si="19"/>
         <v>3.8465023040771484</v>
       </c>
-      <c r="E58" s="12">
+      <c r="E58" s="6">
         <f t="shared" si="20"/>
         <v>-5.116308331489563</v>
       </c>
@@ -6957,18 +6953,18 @@
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B59" s="11">
+      <c r="B59" s="5">
         <v>4</v>
       </c>
-      <c r="C59" s="12">
+      <c r="C59" s="6">
         <f t="shared" si="18"/>
         <v>3.044237494468689</v>
       </c>
-      <c r="D59" s="12">
+      <c r="D59" s="6">
         <f t="shared" si="19"/>
         <v>3.9605554193258286</v>
       </c>
-      <c r="E59" s="12">
+      <c r="E59" s="6">
         <f t="shared" si="20"/>
         <v>-4.9832493485882878</v>
       </c>
@@ -6986,18 +6982,18 @@
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B60" s="11">
+      <c r="B60" s="5">
         <v>5</v>
       </c>
-      <c r="C60" s="12">
+      <c r="C60" s="6">
         <f t="shared" si="18"/>
         <v>3.0259199207648635</v>
       </c>
-      <c r="D60" s="12">
+      <c r="D60" s="6">
         <f t="shared" si="19"/>
         <v>3.9907957980176434</v>
       </c>
-      <c r="E60" s="12">
+      <c r="E60" s="6">
         <f t="shared" si="20"/>
         <v>-5.0070639759724145</v>
       </c>
@@ -7015,18 +7011,18 @@
       </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B61" s="11">
+      <c r="B61" s="5">
         <v>6</v>
       </c>
-      <c r="C61" s="12">
+      <c r="C61" s="6">
         <f t="shared" si="18"/>
         <v>3.0021489591672434</v>
       </c>
-      <c r="D61" s="12">
+      <c r="D61" s="6">
         <f t="shared" si="19"/>
         <v>3.9980789087849189</v>
       </c>
-      <c r="E61" s="12">
+      <c r="E61" s="6">
         <f t="shared" si="20"/>
         <v>-4.9988343470116092</v>
       </c>
@@ -7044,18 +7040,18 @@
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B62" s="11">
+      <c r="B62" s="5">
         <v>7</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C62" s="6">
         <f t="shared" si="18"/>
         <v>3.0012637832223277</v>
       </c>
-      <c r="D62" s="12">
+      <c r="D62" s="6">
         <f t="shared" si="19"/>
         <v>3.9996597425917102</v>
       </c>
-      <c r="E62" s="12">
+      <c r="E62" s="6">
         <f t="shared" si="20"/>
         <v>-5.0003977436871878</v>
       </c>
@@ -7073,59 +7069,59 @@
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B63" s="22">
+      <c r="B63" s="13">
         <v>8</v>
       </c>
-      <c r="C63" s="24">
+      <c r="C63" s="15">
         <f t="shared" si="18"/>
         <v>3.0000030455146898</v>
       </c>
-      <c r="D63" s="24">
+      <c r="D63" s="15">
         <f t="shared" si="19"/>
         <v>3.999957914279805</v>
       </c>
-      <c r="E63" s="24">
+      <c r="E63" s="15">
         <f t="shared" si="20"/>
         <v>-4.9999137158657643</v>
       </c>
-      <c r="F63" s="25">
+      <c r="F63" s="16">
         <f t="shared" si="21"/>
         <v>4.202454759247114E-4</v>
       </c>
-      <c r="G63" s="25">
+      <c r="G63" s="16">
         <f t="shared" si="22"/>
         <v>7.4543706330082118E-5</v>
       </c>
-      <c r="H63" s="25">
+      <c r="H63" s="16">
         <f t="shared" si="23"/>
         <v>9.6807234870397365E-5</v>
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B64" s="22">
+      <c r="B64" s="13">
         <v>9</v>
       </c>
-      <c r="C64" s="24">
+      <c r="C64" s="15">
         <f t="shared" si="18"/>
         <v>3.0000386939840102</v>
       </c>
-      <c r="D64" s="24">
+      <c r="D64" s="15">
         <f t="shared" si="19"/>
         <v>4.0000012096119884</v>
       </c>
-      <c r="E64" s="24">
+      <c r="E64" s="15">
         <f t="shared" si="20"/>
         <v>-5.0000211930298128</v>
       </c>
-      <c r="F64" s="25">
+      <c r="F64" s="16">
         <f t="shared" si="21"/>
         <v>1.188266984421122E-5</v>
       </c>
-      <c r="G64" s="25">
+      <c r="G64" s="16">
         <f t="shared" si="22"/>
         <v>1.08238297726891E-5</v>
       </c>
-      <c r="H64" s="25">
+      <c r="H64" s="16">
         <f t="shared" si="23"/>
         <v>2.1495341699431503E-5</v>
       </c>
